--- a/IT23846586-Assignment 1 - Test cases.xlsx
+++ b/IT23846586-Assignment 1 - Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive D\ITPM\assignment01\test_automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive D\ITPM\assingment 01-submitted\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604C98D3-C589-4941-A7FE-AB49C16D09EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293E4210-DEE2-4BEB-A0DA-CE4CB7C1E8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -947,22 +947,29 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -973,6 +980,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -982,16 +992,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1311,2886 +1311,3122 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="4" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="17" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="4" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="4" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="G14" s="20" t="s">
+      <c r="F14" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="4" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="4" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="9" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="G22" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="H22" s="4" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G26" s="20" t="s">
+      <c r="G26" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="H26" s="20" t="s">
+      <c r="H26" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="5" t="s">
         <v>35</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="H30" s="20" t="s">
+      <c r="H30" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G34" s="20" t="s">
+      <c r="G34" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="H34" s="20" t="s">
+      <c r="H34" s="4" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="5" t="s">
         <v>167</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G38" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="H38" s="20" t="s">
+      <c r="H38" s="4" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="5" t="s">
         <v>44</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="20" t="s">
+      <c r="G42" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="H42" s="20" t="s">
+      <c r="H42" s="4" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="9" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G46" s="20" t="s">
+      <c r="G46" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="H46" s="20" t="s">
+      <c r="H46" s="4" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G50" s="20" t="s">
+      <c r="G50" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="H50" s="20" t="s">
+      <c r="H50" s="4" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C54" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G54" s="20" t="s">
+      <c r="G54" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="H54" s="20" t="s">
+      <c r="H54" s="4" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="5" t="s">
         <v>169</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G58" s="20" t="s">
+      <c r="G58" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="H58" s="20" t="s">
+      <c r="H58" s="4" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="9" t="s">
         <v>58</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E62" s="5" t="s">
         <v>208</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G62" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="H62" s="20" t="s">
+      <c r="H62" s="4" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
     </row>
     <row r="64" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
     </row>
     <row r="65" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="9" t="s">
         <v>61</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="5" t="s">
         <v>64</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G66" s="20" t="s">
+      <c r="G66" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="H66" s="20" t="s">
+      <c r="H66" s="4" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
     </row>
     <row r="69" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C70" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G70" s="20" t="s">
+      <c r="G70" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="H70" s="20" t="s">
+      <c r="H70" s="4" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
     </row>
     <row r="74" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="9" t="s">
         <v>68</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="E74" s="5" t="s">
         <v>70</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G74" s="20" t="s">
+      <c r="G74" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="H74" s="20" t="s">
+      <c r="H74" s="4" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
     </row>
     <row r="76" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="20"/>
-      <c r="H76" s="20"/>
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="20"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
     </row>
     <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="9" t="s">
         <v>71</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C78" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C78" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="5" t="s">
         <v>171</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G78" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="H78" s="20" t="s">
+      <c r="H78" s="4" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
     </row>
     <row r="80" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="20"/>
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
     </row>
     <row r="81" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="20"/>
-      <c r="H81" s="20"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="9" t="s">
         <v>72</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C82" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C82" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="5" t="s">
         <v>173</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G82" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="H82" s="20" t="s">
+      <c r="H82" s="4" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="5"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
     </row>
     <row r="84" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
     </row>
     <row r="85" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="20"/>
-      <c r="H85" s="20"/>
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
     </row>
     <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C86" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C86" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D86" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="E86" s="5" t="s">
         <v>199</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G86" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G86" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="H86" s="20" t="s">
+      <c r="H86" s="4" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
     </row>
     <row r="88" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="5"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="20"/>
-      <c r="H88" s="20"/>
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
     </row>
     <row r="89" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="20"/>
-      <c r="H89" s="20"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
     </row>
     <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D90" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E90" s="7" t="s">
+      <c r="E90" s="5" t="s">
         <v>209</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G90" s="20" t="s">
+      <c r="G90" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="H90" s="20" t="s">
+      <c r="H90" s="4" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="20"/>
-      <c r="H91" s="20"/>
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
     </row>
     <row r="92" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-      <c r="G92" s="20"/>
-      <c r="H92" s="20"/>
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
     </row>
     <row r="93" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="20"/>
-      <c r="H93" s="20"/>
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
     </row>
     <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="9" t="s">
         <v>77</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C94" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C94" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="D94" s="7" t="s">
+      <c r="D94" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="5" t="s">
         <v>200</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G94" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="H94" s="20" t="s">
+      <c r="H94" s="4" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="5"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="20"/>
-      <c r="H95" s="20"/>
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
     </row>
     <row r="96" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="20"/>
-      <c r="H96" s="20"/>
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
     </row>
     <row r="97" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="20"/>
-      <c r="H97" s="20"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
     </row>
     <row r="98" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="9" t="s">
         <v>78</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C98" s="9" t="s">
+      <c r="C98" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="D98" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E98" s="7" t="s">
+      <c r="E98" s="5" t="s">
         <v>81</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G98" s="20" t="s">
+      <c r="G98" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="H98" s="20" t="s">
+      <c r="H98" s="4" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="20"/>
-      <c r="H99" s="20"/>
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
     </row>
     <row r="100" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="5"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
     </row>
     <row r="101" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="20"/>
-      <c r="H101" s="20"/>
+      <c r="A101" s="7"/>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
     </row>
     <row r="102" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="9" t="s">
         <v>82</v>
       </c>
       <c r="B102" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C102" s="9" t="s">
+      <c r="C102" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E102" s="7" t="s">
+      <c r="E102" s="5" t="s">
         <v>85</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G102" s="20" t="s">
+      <c r="G102" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="H102" s="20" t="s">
+      <c r="H102" s="4" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
     </row>
     <row r="104" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="5"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="20"/>
-      <c r="H104" s="20"/>
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
     </row>
     <row r="105" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="20"/>
-      <c r="H105" s="20"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
     </row>
     <row r="106" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C106" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C106" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E106" s="7" t="s">
+      <c r="E106" s="5" t="s">
         <v>201</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G106" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="H106" s="20" t="s">
+      <c r="H106" s="4" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="5"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
-      <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-      <c r="G107" s="20"/>
-      <c r="H107" s="20"/>
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
     </row>
     <row r="108" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="5"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-      <c r="G108" s="20"/>
-      <c r="H108" s="20"/>
+      <c r="A108" s="6"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
     </row>
     <row r="109" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="20"/>
-      <c r="H109" s="20"/>
+      <c r="A109" s="7"/>
+      <c r="B109" s="7"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
     </row>
     <row r="110" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="9" t="s">
         <v>87</v>
       </c>
       <c r="B110" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C110" s="9" t="s">
+      <c r="C110" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D110" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E110" s="7" t="s">
+      <c r="E110" s="5" t="s">
         <v>90</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G110" s="20" t="s">
+      <c r="G110" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="H110" s="20" t="s">
+      <c r="H110" s="4" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="5"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-      <c r="G111" s="20"/>
-      <c r="H111" s="20"/>
+      <c r="A111" s="6"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
     </row>
     <row r="112" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="5"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-      <c r="G112" s="20"/>
-      <c r="H112" s="20"/>
+      <c r="A112" s="6"/>
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
     </row>
     <row r="113" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
     </row>
     <row r="114" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="9" t="s">
         <v>91</v>
       </c>
       <c r="B114" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C114" s="9" t="s">
+      <c r="C114" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E114" s="7" t="s">
+      <c r="E114" s="5" t="s">
         <v>94</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G114" s="20" t="s">
+      <c r="G114" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="H114" s="20" t="s">
+      <c r="H114" s="4" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="5"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
-      <c r="G115" s="20"/>
-      <c r="H115" s="20"/>
+      <c r="A115" s="6"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
     </row>
     <row r="116" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="5"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-      <c r="G116" s="20"/>
-      <c r="H116" s="20"/>
+      <c r="A116" s="6"/>
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
     </row>
     <row r="117" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="20"/>
-      <c r="H117" s="20"/>
+      <c r="A117" s="7"/>
+      <c r="B117" s="7"/>
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
     </row>
     <row r="118" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="9" t="s">
         <v>95</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C118" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C118" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="D118" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E118" s="7" t="s">
+      <c r="E118" s="5" t="s">
         <v>202</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G118" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G118" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H118" s="20" t="s">
+      <c r="H118" s="4" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="5"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
-      <c r="G119" s="20"/>
-      <c r="H119" s="20"/>
+      <c r="A119" s="6"/>
+      <c r="B119" s="6"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
     </row>
     <row r="120" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="5"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="5"/>
-      <c r="G120" s="20"/>
-      <c r="H120" s="20"/>
+      <c r="A120" s="6"/>
+      <c r="B120" s="6"/>
+      <c r="C120" s="6"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4"/>
     </row>
     <row r="121" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="20"/>
-      <c r="H121" s="20"/>
+      <c r="A121" s="7"/>
+      <c r="B121" s="7"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
     </row>
     <row r="122" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="9" t="s">
         <v>96</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C122" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C122" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="D122" s="7" t="s">
+      <c r="D122" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="E122" s="7" t="s">
+      <c r="E122" s="5" t="s">
         <v>203</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G122" s="20" t="s">
+      <c r="G122" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="H122" s="20" t="s">
+      <c r="H122" s="4" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="5"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
-      <c r="D123" s="5"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="5"/>
-      <c r="G123" s="20"/>
-      <c r="H123" s="20"/>
+      <c r="A123" s="6"/>
+      <c r="B123" s="6"/>
+      <c r="C123" s="6"/>
+      <c r="D123" s="6"/>
+      <c r="E123" s="6"/>
+      <c r="F123" s="6"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
     </row>
     <row r="124" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="5"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="5"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="5"/>
-      <c r="G124" s="20"/>
-      <c r="H124" s="20"/>
+      <c r="A124" s="6"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="6"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="4"/>
+      <c r="H124" s="4"/>
     </row>
     <row r="125" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="20"/>
-      <c r="H125" s="20"/>
+      <c r="A125" s="7"/>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="4"/>
+      <c r="H125" s="4"/>
     </row>
     <row r="126" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="9" t="s">
         <v>97</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C126" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C126" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="D126" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E126" s="7" t="s">
+      <c r="E126" s="5" t="s">
         <v>204</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G126" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G126" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="H126" s="20" t="s">
+      <c r="H126" s="4" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="5"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="5"/>
-      <c r="G127" s="20"/>
-      <c r="H127" s="20"/>
+      <c r="A127" s="6"/>
+      <c r="B127" s="6"/>
+      <c r="C127" s="6"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="4"/>
+      <c r="H127" s="4"/>
     </row>
     <row r="128" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="5"/>
-      <c r="B128" s="5"/>
-      <c r="C128" s="5"/>
-      <c r="D128" s="5"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="5"/>
-      <c r="G128" s="20"/>
-      <c r="H128" s="20"/>
+      <c r="A128" s="6"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="6"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="4"/>
+      <c r="H128" s="4"/>
     </row>
     <row r="129" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="20"/>
+      <c r="A129" s="7"/>
+      <c r="B129" s="7"/>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
+      <c r="G129" s="4"/>
+      <c r="H129" s="4"/>
     </row>
     <row r="130" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="9" t="s">
         <v>98</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C130" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C130" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="D130" s="7" t="s">
+      <c r="D130" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E130" s="7" t="s">
+      <c r="E130" s="5" t="s">
         <v>187</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G130" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="H130" s="20" t="s">
+      <c r="H130" s="4" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="5"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="5"/>
-      <c r="D131" s="5"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="5"/>
-      <c r="G131" s="20"/>
-      <c r="H131" s="20"/>
+      <c r="A131" s="6"/>
+      <c r="B131" s="6"/>
+      <c r="C131" s="6"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="6"/>
+      <c r="F131" s="6"/>
+      <c r="G131" s="4"/>
+      <c r="H131" s="4"/>
     </row>
     <row r="132" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="5"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="5"/>
-      <c r="D132" s="5"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="5"/>
-      <c r="G132" s="20"/>
-      <c r="H132" s="20"/>
+      <c r="A132" s="6"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="4"/>
+      <c r="H132" s="4"/>
     </row>
     <row r="133" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="20"/>
-      <c r="H133" s="20"/>
+      <c r="A133" s="7"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="4"/>
+      <c r="H133" s="4"/>
     </row>
     <row r="134" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="9" t="s">
         <v>99</v>
       </c>
       <c r="B134" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C134" s="9" t="s">
+      <c r="C134" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D134" s="7" t="s">
+      <c r="D134" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E134" s="7" t="s">
+      <c r="E134" s="5" t="s">
         <v>102</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G134" s="20" t="s">
+      <c r="G134" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="H134" s="20" t="s">
+      <c r="H134" s="4" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="5"/>
-      <c r="B135" s="5"/>
-      <c r="C135" s="5"/>
-      <c r="D135" s="5"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="5"/>
-      <c r="G135" s="20"/>
-      <c r="H135" s="20"/>
+      <c r="A135" s="6"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="6"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="4"/>
+      <c r="H135" s="4"/>
     </row>
     <row r="136" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="5"/>
-      <c r="B136" s="5"/>
-      <c r="C136" s="5"/>
-      <c r="D136" s="5"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="5"/>
-      <c r="G136" s="20"/>
-      <c r="H136" s="20"/>
+      <c r="A136" s="6"/>
+      <c r="B136" s="6"/>
+      <c r="C136" s="6"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4"/>
     </row>
     <row r="137" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="20"/>
-      <c r="H137" s="20"/>
+      <c r="A137" s="7"/>
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="4"/>
+      <c r="H137" s="4"/>
     </row>
     <row r="138" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="9" t="s">
         <v>103</v>
       </c>
       <c r="B138" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C138" s="9" t="s">
+      <c r="C138" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D138" s="7" t="s">
+      <c r="D138" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E138" s="7" t="s">
+      <c r="E138" s="5" t="s">
         <v>106</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G138" s="20" t="s">
+      <c r="G138" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="H138" s="20" t="s">
+      <c r="H138" s="4" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="5"/>
-      <c r="B139" s="5"/>
-      <c r="C139" s="5"/>
-      <c r="D139" s="5"/>
-      <c r="E139" s="5"/>
-      <c r="F139" s="5"/>
-      <c r="G139" s="20"/>
-      <c r="H139" s="20"/>
+      <c r="A139" s="6"/>
+      <c r="B139" s="6"/>
+      <c r="C139" s="6"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4"/>
     </row>
     <row r="140" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="5"/>
-      <c r="B140" s="5"/>
-      <c r="C140" s="5"/>
-      <c r="D140" s="5"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="5"/>
-      <c r="G140" s="20"/>
-      <c r="H140" s="20"/>
+      <c r="A140" s="6"/>
+      <c r="B140" s="6"/>
+      <c r="C140" s="6"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="4"/>
+      <c r="H140" s="4"/>
     </row>
     <row r="141" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="20"/>
-      <c r="H141" s="20"/>
+      <c r="A141" s="7"/>
+      <c r="B141" s="7"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
     </row>
     <row r="142" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="9" t="s">
         <v>107</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C142" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C142" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="D142" s="7" t="s">
+      <c r="D142" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E142" s="7" t="s">
+      <c r="E142" s="5" t="s">
         <v>205</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G142" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G142" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="H142" s="20" t="s">
+      <c r="H142" s="4" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="5"/>
-      <c r="B143" s="5"/>
-      <c r="C143" s="5"/>
-      <c r="D143" s="5"/>
-      <c r="E143" s="5"/>
-      <c r="F143" s="5"/>
-      <c r="G143" s="20"/>
-      <c r="H143" s="20"/>
+      <c r="A143" s="6"/>
+      <c r="B143" s="6"/>
+      <c r="C143" s="6"/>
+      <c r="D143" s="6"/>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="4"/>
+      <c r="H143" s="4"/>
     </row>
     <row r="144" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="5"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="5"/>
-      <c r="D144" s="5"/>
-      <c r="E144" s="5"/>
-      <c r="F144" s="5"/>
-      <c r="G144" s="20"/>
-      <c r="H144" s="20"/>
+      <c r="A144" s="6"/>
+      <c r="B144" s="6"/>
+      <c r="C144" s="6"/>
+      <c r="D144" s="6"/>
+      <c r="E144" s="6"/>
+      <c r="F144" s="6"/>
+      <c r="G144" s="4"/>
+      <c r="H144" s="4"/>
     </row>
     <row r="145" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="20"/>
-      <c r="H145" s="20"/>
+      <c r="A145" s="7"/>
+      <c r="B145" s="7"/>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7"/>
+      <c r="G145" s="4"/>
+      <c r="H145" s="4"/>
     </row>
     <row r="146" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="4" t="s">
+      <c r="A146" s="9" t="s">
         <v>108</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C146" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C146" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="D146" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E146" s="7" t="s">
+      <c r="E146" s="5" t="s">
         <v>111</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G146" s="20" t="s">
+      <c r="G146" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="H146" s="20" t="s">
+      <c r="H146" s="4" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="5"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="5"/>
-      <c r="D147" s="5"/>
-      <c r="E147" s="5"/>
-      <c r="F147" s="5"/>
-      <c r="G147" s="20"/>
-      <c r="H147" s="20"/>
+      <c r="A147" s="6"/>
+      <c r="B147" s="6"/>
+      <c r="C147" s="6"/>
+      <c r="D147" s="6"/>
+      <c r="E147" s="6"/>
+      <c r="F147" s="6"/>
+      <c r="G147" s="4"/>
+      <c r="H147" s="4"/>
     </row>
     <row r="148" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="5"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="5"/>
-      <c r="D148" s="5"/>
-      <c r="E148" s="5"/>
-      <c r="F148" s="5"/>
-      <c r="G148" s="20"/>
-      <c r="H148" s="20"/>
+      <c r="A148" s="6"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="6"/>
+      <c r="E148" s="6"/>
+      <c r="F148" s="6"/>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4"/>
     </row>
     <row r="149" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="20"/>
-      <c r="H149" s="20"/>
+      <c r="A149" s="7"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
     </row>
     <row r="150" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="4" t="s">
+      <c r="A150" s="9" t="s">
         <v>112</v>
       </c>
       <c r="B150" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C150" s="9" t="s">
+      <c r="C150" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="D150" s="7" t="s">
+      <c r="D150" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E150" s="7" t="s">
+      <c r="E150" s="5" t="s">
         <v>115</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G150" s="20" t="s">
+      <c r="G150" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="H150" s="20" t="s">
+      <c r="H150" s="4" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="5"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="5"/>
-      <c r="D151" s="5"/>
-      <c r="E151" s="5"/>
-      <c r="F151" s="5"/>
-      <c r="G151" s="20"/>
-      <c r="H151" s="20"/>
+      <c r="A151" s="6"/>
+      <c r="B151" s="6"/>
+      <c r="C151" s="6"/>
+      <c r="D151" s="6"/>
+      <c r="E151" s="6"/>
+      <c r="F151" s="6"/>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4"/>
     </row>
     <row r="152" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="5"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="5"/>
-      <c r="D152" s="5"/>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5"/>
-      <c r="G152" s="20"/>
-      <c r="H152" s="20"/>
+      <c r="A152" s="6"/>
+      <c r="B152" s="6"/>
+      <c r="C152" s="6"/>
+      <c r="D152" s="6"/>
+      <c r="E152" s="6"/>
+      <c r="F152" s="6"/>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4"/>
     </row>
     <row r="153" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="20"/>
-      <c r="H153" s="20"/>
+      <c r="A153" s="7"/>
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
     </row>
     <row r="154" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="4" t="s">
+      <c r="A154" s="9" t="s">
         <v>116</v>
       </c>
       <c r="B154" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C154" s="9" t="s">
+      <c r="C154" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D154" s="7" t="s">
+      <c r="D154" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E154" s="7" t="s">
+      <c r="E154" s="5" t="s">
         <v>119</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G154" s="20" t="s">
+      <c r="G154" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="H154" s="20" t="s">
+      <c r="H154" s="4" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="5"/>
-      <c r="B155" s="5"/>
-      <c r="C155" s="5"/>
-      <c r="D155" s="5"/>
-      <c r="E155" s="5"/>
-      <c r="F155" s="5"/>
-      <c r="G155" s="20"/>
-      <c r="H155" s="20"/>
+      <c r="A155" s="6"/>
+      <c r="B155" s="6"/>
+      <c r="C155" s="6"/>
+      <c r="D155" s="6"/>
+      <c r="E155" s="6"/>
+      <c r="F155" s="6"/>
+      <c r="G155" s="4"/>
+      <c r="H155" s="4"/>
     </row>
     <row r="156" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="5"/>
-      <c r="B156" s="5"/>
-      <c r="C156" s="5"/>
-      <c r="D156" s="5"/>
-      <c r="E156" s="5"/>
-      <c r="F156" s="5"/>
-      <c r="G156" s="20"/>
-      <c r="H156" s="20"/>
+      <c r="A156" s="6"/>
+      <c r="B156" s="6"/>
+      <c r="C156" s="6"/>
+      <c r="D156" s="6"/>
+      <c r="E156" s="6"/>
+      <c r="F156" s="6"/>
+      <c r="G156" s="4"/>
+      <c r="H156" s="4"/>
     </row>
     <row r="157" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="20"/>
-      <c r="H157" s="20"/>
+      <c r="A157" s="7"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="4"/>
+      <c r="H157" s="4"/>
     </row>
     <row r="158" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="9" t="s">
         <v>120</v>
       </c>
       <c r="B158" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C158" s="9" t="s">
+      <c r="C158" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="D158" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E158" s="7" t="s">
+      <c r="E158" s="5" t="s">
         <v>123</v>
       </c>
       <c r="F158" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G158" s="20" t="s">
+      <c r="G158" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="H158" s="20" t="s">
+      <c r="H158" s="4" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="5"/>
-      <c r="B159" s="5"/>
-      <c r="C159" s="5"/>
-      <c r="D159" s="5"/>
-      <c r="E159" s="5"/>
-      <c r="F159" s="5"/>
-      <c r="G159" s="20"/>
-      <c r="H159" s="20"/>
+      <c r="A159" s="6"/>
+      <c r="B159" s="6"/>
+      <c r="C159" s="6"/>
+      <c r="D159" s="6"/>
+      <c r="E159" s="6"/>
+      <c r="F159" s="6"/>
+      <c r="G159" s="4"/>
+      <c r="H159" s="4"/>
     </row>
     <row r="160" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="5"/>
-      <c r="B160" s="5"/>
-      <c r="C160" s="5"/>
-      <c r="D160" s="5"/>
-      <c r="E160" s="5"/>
-      <c r="F160" s="5"/>
-      <c r="G160" s="20"/>
-      <c r="H160" s="20"/>
+      <c r="A160" s="6"/>
+      <c r="B160" s="6"/>
+      <c r="C160" s="6"/>
+      <c r="D160" s="6"/>
+      <c r="E160" s="6"/>
+      <c r="F160" s="6"/>
+      <c r="G160" s="4"/>
+      <c r="H160" s="4"/>
     </row>
     <row r="161" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="6"/>
-      <c r="F161" s="6"/>
-      <c r="G161" s="20"/>
-      <c r="H161" s="20"/>
+      <c r="A161" s="7"/>
+      <c r="B161" s="7"/>
+      <c r="C161" s="7"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="7"/>
+      <c r="G161" s="4"/>
+      <c r="H161" s="4"/>
     </row>
     <row r="162" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="4" t="s">
+      <c r="A162" s="9" t="s">
         <v>124</v>
       </c>
       <c r="B162" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C162" s="9" t="s">
+      <c r="C162" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D162" s="7" t="s">
+      <c r="D162" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E162" s="7" t="s">
+      <c r="E162" s="5" t="s">
         <v>127</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G162" s="20" t="s">
+      <c r="G162" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="H162" s="20" t="s">
+      <c r="H162" s="4" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="5"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="5"/>
-      <c r="D163" s="5"/>
-      <c r="E163" s="5"/>
-      <c r="F163" s="5"/>
-      <c r="G163" s="20"/>
-      <c r="H163" s="20"/>
+      <c r="A163" s="6"/>
+      <c r="B163" s="6"/>
+      <c r="C163" s="6"/>
+      <c r="D163" s="6"/>
+      <c r="E163" s="6"/>
+      <c r="F163" s="6"/>
+      <c r="G163" s="4"/>
+      <c r="H163" s="4"/>
     </row>
     <row r="164" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="5"/>
-      <c r="B164" s="5"/>
-      <c r="C164" s="5"/>
-      <c r="D164" s="5"/>
-      <c r="E164" s="5"/>
-      <c r="F164" s="5"/>
-      <c r="G164" s="20"/>
-      <c r="H164" s="20"/>
+      <c r="A164" s="6"/>
+      <c r="B164" s="6"/>
+      <c r="C164" s="6"/>
+      <c r="D164" s="6"/>
+      <c r="E164" s="6"/>
+      <c r="F164" s="6"/>
+      <c r="G164" s="4"/>
+      <c r="H164" s="4"/>
     </row>
     <row r="165" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
-      <c r="C165" s="6"/>
-      <c r="D165" s="6"/>
-      <c r="E165" s="6"/>
-      <c r="F165" s="6"/>
-      <c r="G165" s="20"/>
-      <c r="H165" s="20"/>
+      <c r="A165" s="7"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="4"/>
+      <c r="H165" s="4"/>
     </row>
     <row r="166" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="4" t="s">
+      <c r="A166" s="9" t="s">
         <v>128</v>
       </c>
       <c r="B166" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C166" s="9" t="s">
+      <c r="C166" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D166" s="7" t="s">
+      <c r="D166" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E166" s="7" t="s">
+      <c r="E166" s="5" t="s">
         <v>131</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G166" s="20" t="s">
+      <c r="G166" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="H166" s="20" t="s">
+      <c r="H166" s="4" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="5"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="5"/>
-      <c r="D167" s="5"/>
-      <c r="E167" s="5"/>
-      <c r="F167" s="5"/>
-      <c r="G167" s="20"/>
-      <c r="H167" s="20"/>
+      <c r="A167" s="6"/>
+      <c r="B167" s="6"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="6"/>
+      <c r="E167" s="6"/>
+      <c r="F167" s="6"/>
+      <c r="G167" s="4"/>
+      <c r="H167" s="4"/>
     </row>
     <row r="168" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="5"/>
-      <c r="B168" s="5"/>
-      <c r="C168" s="5"/>
-      <c r="D168" s="5"/>
-      <c r="E168" s="5"/>
-      <c r="F168" s="5"/>
-      <c r="G168" s="20"/>
-      <c r="H168" s="20"/>
+      <c r="A168" s="6"/>
+      <c r="B168" s="6"/>
+      <c r="C168" s="6"/>
+      <c r="D168" s="6"/>
+      <c r="E168" s="6"/>
+      <c r="F168" s="6"/>
+      <c r="G168" s="4"/>
+      <c r="H168" s="4"/>
     </row>
     <row r="169" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="20"/>
-      <c r="H169" s="20"/>
+      <c r="A169" s="7"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
+      <c r="G169" s="4"/>
+      <c r="H169" s="4"/>
     </row>
     <row r="170" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="9" t="s">
         <v>132</v>
       </c>
       <c r="B170" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C170" s="9" t="s">
+      <c r="C170" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D170" s="7" t="s">
+      <c r="D170" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E170" s="7" t="s">
+      <c r="E170" s="5" t="s">
         <v>135</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G170" s="20" t="s">
+      <c r="G170" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="H170" s="20" t="s">
+      <c r="H170" s="4" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="5"/>
-      <c r="B171" s="5"/>
-      <c r="C171" s="5"/>
-      <c r="D171" s="5"/>
-      <c r="E171" s="5"/>
-      <c r="F171" s="5"/>
-      <c r="G171" s="20"/>
-      <c r="H171" s="20"/>
+      <c r="A171" s="6"/>
+      <c r="B171" s="6"/>
+      <c r="C171" s="6"/>
+      <c r="D171" s="6"/>
+      <c r="E171" s="6"/>
+      <c r="F171" s="6"/>
+      <c r="G171" s="4"/>
+      <c r="H171" s="4"/>
     </row>
     <row r="172" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="5"/>
-      <c r="B172" s="5"/>
-      <c r="C172" s="5"/>
-      <c r="D172" s="5"/>
-      <c r="E172" s="5"/>
-      <c r="F172" s="5"/>
-      <c r="G172" s="20"/>
-      <c r="H172" s="20"/>
+      <c r="A172" s="6"/>
+      <c r="B172" s="6"/>
+      <c r="C172" s="6"/>
+      <c r="D172" s="6"/>
+      <c r="E172" s="6"/>
+      <c r="F172" s="6"/>
+      <c r="G172" s="4"/>
+      <c r="H172" s="4"/>
     </row>
     <row r="173" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="20"/>
-      <c r="H173" s="20"/>
+      <c r="A173" s="7"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7"/>
+      <c r="G173" s="4"/>
+      <c r="H173" s="4"/>
     </row>
     <row r="174" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="4" t="s">
+      <c r="A174" s="9" t="s">
         <v>136</v>
       </c>
       <c r="B174" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C174" s="9" t="s">
+      <c r="C174" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="D174" s="7" t="s">
+      <c r="D174" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="E174" s="7" t="s">
+      <c r="E174" s="5" t="s">
         <v>139</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G174" s="20" t="s">
+      <c r="G174" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="H174" s="20" t="s">
+      <c r="H174" s="4" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="5"/>
-      <c r="B175" s="5"/>
-      <c r="C175" s="5"/>
-      <c r="D175" s="5"/>
-      <c r="E175" s="5"/>
-      <c r="F175" s="5"/>
-      <c r="G175" s="20"/>
-      <c r="H175" s="20"/>
+      <c r="A175" s="6"/>
+      <c r="B175" s="6"/>
+      <c r="C175" s="6"/>
+      <c r="D175" s="6"/>
+      <c r="E175" s="6"/>
+      <c r="F175" s="6"/>
+      <c r="G175" s="4"/>
+      <c r="H175" s="4"/>
     </row>
     <row r="176" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="5"/>
-      <c r="B176" s="5"/>
-      <c r="C176" s="5"/>
-      <c r="D176" s="5"/>
-      <c r="E176" s="5"/>
-      <c r="F176" s="5"/>
-      <c r="G176" s="20"/>
-      <c r="H176" s="20"/>
+      <c r="A176" s="6"/>
+      <c r="B176" s="6"/>
+      <c r="C176" s="6"/>
+      <c r="D176" s="6"/>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6"/>
+      <c r="G176" s="4"/>
+      <c r="H176" s="4"/>
     </row>
     <row r="177" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="20"/>
-      <c r="H177" s="20"/>
+      <c r="A177" s="7"/>
+      <c r="B177" s="7"/>
+      <c r="C177" s="7"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
+      <c r="G177" s="4"/>
+      <c r="H177" s="4"/>
     </row>
     <row r="178" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="4" t="s">
+      <c r="A178" s="9" t="s">
         <v>140</v>
       </c>
       <c r="B178" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C178" s="9" t="s">
+      <c r="C178" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D178" s="7" t="s">
+      <c r="D178" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E178" s="7" t="s">
+      <c r="E178" s="5" t="s">
         <v>143</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G178" s="20" t="s">
+      <c r="G178" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="H178" s="20" t="s">
+      <c r="H178" s="4" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="5"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="5"/>
-      <c r="D179" s="5"/>
-      <c r="E179" s="5"/>
-      <c r="F179" s="5"/>
-      <c r="G179" s="20"/>
-      <c r="H179" s="20"/>
+      <c r="A179" s="6"/>
+      <c r="B179" s="6"/>
+      <c r="C179" s="6"/>
+      <c r="D179" s="6"/>
+      <c r="E179" s="6"/>
+      <c r="F179" s="6"/>
+      <c r="G179" s="4"/>
+      <c r="H179" s="4"/>
     </row>
     <row r="180" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="5"/>
-      <c r="B180" s="5"/>
-      <c r="C180" s="5"/>
-      <c r="D180" s="5"/>
-      <c r="E180" s="5"/>
-      <c r="F180" s="5"/>
-      <c r="G180" s="20"/>
-      <c r="H180" s="20"/>
+      <c r="A180" s="6"/>
+      <c r="B180" s="6"/>
+      <c r="C180" s="6"/>
+      <c r="D180" s="6"/>
+      <c r="E180" s="6"/>
+      <c r="F180" s="6"/>
+      <c r="G180" s="4"/>
+      <c r="H180" s="4"/>
     </row>
     <row r="181" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
-      <c r="G181" s="20"/>
-      <c r="H181" s="20"/>
+      <c r="A181" s="7"/>
+      <c r="B181" s="7"/>
+      <c r="C181" s="7"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="7"/>
+      <c r="F181" s="7"/>
+      <c r="G181" s="4"/>
+      <c r="H181" s="4"/>
     </row>
     <row r="182" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="4" t="s">
+      <c r="A182" s="9" t="s">
         <v>144</v>
       </c>
       <c r="B182" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C182" s="9" t="s">
+      <c r="C182" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="D182" s="7" t="s">
+      <c r="D182" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E182" s="7" t="s">
+      <c r="E182" s="5" t="s">
         <v>147</v>
       </c>
       <c r="F182" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G182" s="20" t="s">
+      <c r="G182" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="H182" s="20" t="s">
+      <c r="H182" s="4" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="5"/>
-      <c r="B183" s="5"/>
-      <c r="C183" s="5"/>
-      <c r="D183" s="5"/>
-      <c r="E183" s="5"/>
-      <c r="F183" s="5"/>
-      <c r="G183" s="20"/>
-      <c r="H183" s="20"/>
+      <c r="A183" s="6"/>
+      <c r="B183" s="6"/>
+      <c r="C183" s="6"/>
+      <c r="D183" s="6"/>
+      <c r="E183" s="6"/>
+      <c r="F183" s="6"/>
+      <c r="G183" s="4"/>
+      <c r="H183" s="4"/>
     </row>
     <row r="184" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="5"/>
-      <c r="B184" s="5"/>
-      <c r="C184" s="5"/>
-      <c r="D184" s="5"/>
-      <c r="E184" s="5"/>
-      <c r="F184" s="5"/>
-      <c r="G184" s="20"/>
-      <c r="H184" s="20"/>
+      <c r="A184" s="6"/>
+      <c r="B184" s="6"/>
+      <c r="C184" s="6"/>
+      <c r="D184" s="6"/>
+      <c r="E184" s="6"/>
+      <c r="F184" s="6"/>
+      <c r="G184" s="4"/>
+      <c r="H184" s="4"/>
     </row>
     <row r="185" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="20"/>
-      <c r="H185" s="20"/>
+      <c r="A185" s="7"/>
+      <c r="B185" s="7"/>
+      <c r="C185" s="7"/>
+      <c r="D185" s="7"/>
+      <c r="E185" s="7"/>
+      <c r="F185" s="7"/>
+      <c r="G185" s="4"/>
+      <c r="H185" s="4"/>
     </row>
     <row r="186" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="4" t="s">
+      <c r="A186" s="9" t="s">
         <v>148</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C186" s="9" t="s">
+      <c r="C186" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="D186" s="7" t="s">
+      <c r="D186" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E186" s="7" t="s">
+      <c r="E186" s="5" t="s">
         <v>151</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G186" s="20" t="s">
+      <c r="G186" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="H186" s="20" t="s">
+      <c r="H186" s="4" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="5"/>
-      <c r="B187" s="5"/>
-      <c r="C187" s="5"/>
-      <c r="D187" s="5"/>
-      <c r="E187" s="5"/>
-      <c r="F187" s="5"/>
-      <c r="G187" s="20"/>
-      <c r="H187" s="20"/>
+      <c r="A187" s="6"/>
+      <c r="B187" s="6"/>
+      <c r="C187" s="6"/>
+      <c r="D187" s="6"/>
+      <c r="E187" s="6"/>
+      <c r="F187" s="6"/>
+      <c r="G187" s="4"/>
+      <c r="H187" s="4"/>
     </row>
     <row r="188" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="5"/>
-      <c r="B188" s="5"/>
-      <c r="C188" s="5"/>
-      <c r="D188" s="5"/>
-      <c r="E188" s="5"/>
-      <c r="F188" s="5"/>
-      <c r="G188" s="20"/>
-      <c r="H188" s="20"/>
+      <c r="A188" s="6"/>
+      <c r="B188" s="6"/>
+      <c r="C188" s="6"/>
+      <c r="D188" s="6"/>
+      <c r="E188" s="6"/>
+      <c r="F188" s="6"/>
+      <c r="G188" s="4"/>
+      <c r="H188" s="4"/>
     </row>
     <row r="189" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="20"/>
-      <c r="H189" s="20"/>
+      <c r="A189" s="7"/>
+      <c r="B189" s="7"/>
+      <c r="C189" s="7"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
+      <c r="G189" s="4"/>
+      <c r="H189" s="4"/>
     </row>
     <row r="190" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="9" t="s">
         <v>152</v>
       </c>
       <c r="B190" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C190" s="9" t="s">
+      <c r="C190" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D190" s="7" t="s">
+      <c r="D190" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E190" s="7" t="s">
+      <c r="E190" s="5" t="s">
         <v>210</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G190" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G190" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="H190" s="20" t="s">
+      <c r="H190" s="4" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="5"/>
-      <c r="B191" s="5"/>
-      <c r="C191" s="5"/>
-      <c r="D191" s="5"/>
-      <c r="E191" s="5"/>
-      <c r="F191" s="5"/>
-      <c r="G191" s="20"/>
-      <c r="H191" s="20"/>
+      <c r="A191" s="6"/>
+      <c r="B191" s="6"/>
+      <c r="C191" s="6"/>
+      <c r="D191" s="6"/>
+      <c r="E191" s="6"/>
+      <c r="F191" s="6"/>
+      <c r="G191" s="4"/>
+      <c r="H191" s="4"/>
     </row>
     <row r="192" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="5"/>
-      <c r="B192" s="5"/>
-      <c r="C192" s="5"/>
-      <c r="D192" s="5"/>
-      <c r="E192" s="5"/>
-      <c r="F192" s="5"/>
-      <c r="G192" s="20"/>
-      <c r="H192" s="20"/>
+      <c r="A192" s="6"/>
+      <c r="B192" s="6"/>
+      <c r="C192" s="6"/>
+      <c r="D192" s="6"/>
+      <c r="E192" s="6"/>
+      <c r="F192" s="6"/>
+      <c r="G192" s="4"/>
+      <c r="H192" s="4"/>
     </row>
     <row r="193" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="6"/>
-      <c r="D193" s="6"/>
-      <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
-      <c r="G193" s="20"/>
-      <c r="H193" s="20"/>
+      <c r="A193" s="7"/>
+      <c r="B193" s="7"/>
+      <c r="C193" s="7"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7"/>
+      <c r="F193" s="7"/>
+      <c r="G193" s="4"/>
+      <c r="H193" s="4"/>
     </row>
     <row r="194" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="4" t="s">
+      <c r="A194" s="9" t="s">
         <v>155</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C194" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C194" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D194" s="7" t="s">
+      <c r="D194" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E194" s="7" t="s">
+      <c r="E194" s="5" t="s">
         <v>158</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G194" s="20" t="s">
+      <c r="G194" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="H194" s="20" t="s">
+      <c r="H194" s="4" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="5"/>
-      <c r="B195" s="5"/>
-      <c r="C195" s="5"/>
-      <c r="D195" s="5"/>
-      <c r="E195" s="5"/>
-      <c r="F195" s="5"/>
-      <c r="G195" s="20"/>
-      <c r="H195" s="20"/>
+      <c r="A195" s="6"/>
+      <c r="B195" s="6"/>
+      <c r="C195" s="6"/>
+      <c r="D195" s="6"/>
+      <c r="E195" s="6"/>
+      <c r="F195" s="6"/>
+      <c r="G195" s="4"/>
+      <c r="H195" s="4"/>
     </row>
     <row r="196" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="5"/>
-      <c r="B196" s="5"/>
-      <c r="C196" s="5"/>
-      <c r="D196" s="5"/>
-      <c r="E196" s="5"/>
-      <c r="F196" s="5"/>
-      <c r="G196" s="20"/>
-      <c r="H196" s="20"/>
+      <c r="A196" s="6"/>
+      <c r="B196" s="6"/>
+      <c r="C196" s="6"/>
+      <c r="D196" s="6"/>
+      <c r="E196" s="6"/>
+      <c r="F196" s="6"/>
+      <c r="G196" s="4"/>
+      <c r="H196" s="4"/>
     </row>
     <row r="197" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="6"/>
-      <c r="D197" s="6"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="20"/>
-      <c r="H197" s="20"/>
+      <c r="A197" s="7"/>
+      <c r="B197" s="7"/>
+      <c r="C197" s="7"/>
+      <c r="D197" s="7"/>
+      <c r="E197" s="7"/>
+      <c r="F197" s="7"/>
+      <c r="G197" s="4"/>
+      <c r="H197" s="4"/>
     </row>
     <row r="198" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="4" t="s">
+      <c r="A198" s="9" t="s">
         <v>159</v>
       </c>
       <c r="B198" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C198" s="9" t="s">
+      <c r="C198" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="D198" s="7" t="s">
+      <c r="D198" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E198" s="7" t="s">
+      <c r="E198" s="5" t="s">
         <v>206</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G198" s="20" t="s">
+      <c r="G198" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="H198" s="20" t="s">
+      <c r="H198" s="4" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="5"/>
-      <c r="B199" s="5"/>
-      <c r="C199" s="5"/>
-      <c r="D199" s="5"/>
-      <c r="E199" s="5"/>
-      <c r="F199" s="5"/>
-      <c r="G199" s="20"/>
-      <c r="H199" s="20"/>
+      <c r="A199" s="6"/>
+      <c r="B199" s="6"/>
+      <c r="C199" s="6"/>
+      <c r="D199" s="6"/>
+      <c r="E199" s="6"/>
+      <c r="F199" s="6"/>
+      <c r="G199" s="4"/>
+      <c r="H199" s="4"/>
     </row>
     <row r="200" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="5"/>
-      <c r="B200" s="5"/>
-      <c r="C200" s="5"/>
-      <c r="D200" s="5"/>
-      <c r="E200" s="5"/>
-      <c r="F200" s="5"/>
-      <c r="G200" s="20"/>
-      <c r="H200" s="20"/>
+      <c r="A200" s="6"/>
+      <c r="B200" s="6"/>
+      <c r="C200" s="6"/>
+      <c r="D200" s="6"/>
+      <c r="E200" s="6"/>
+      <c r="F200" s="6"/>
+      <c r="G200" s="4"/>
+      <c r="H200" s="4"/>
     </row>
     <row r="201" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="6"/>
-      <c r="B201" s="6"/>
-      <c r="C201" s="6"/>
-      <c r="D201" s="6"/>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
-      <c r="G201" s="20"/>
-      <c r="H201" s="20"/>
+      <c r="A201" s="7"/>
+      <c r="B201" s="7"/>
+      <c r="C201" s="7"/>
+      <c r="D201" s="7"/>
+      <c r="E201" s="7"/>
+      <c r="F201" s="7"/>
+      <c r="G201" s="4"/>
+      <c r="H201" s="4"/>
     </row>
     <row r="202" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="4" t="s">
+      <c r="A202" s="9" t="s">
         <v>160</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C202" s="9" t="s">
+      <c r="C202" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D202" s="7" t="s">
+      <c r="D202" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E202" s="7" t="s">
+      <c r="E202" s="5" t="s">
         <v>163</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G202" s="20" t="s">
+      <c r="G202" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="H202" s="20" t="s">
+      <c r="H202" s="4" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="5"/>
-      <c r="B203" s="5"/>
-      <c r="C203" s="5"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="5"/>
-      <c r="F203" s="5"/>
+      <c r="A203" s="6"/>
+      <c r="B203" s="6"/>
+      <c r="C203" s="6"/>
+      <c r="D203" s="6"/>
+      <c r="E203" s="6"/>
+      <c r="F203" s="6"/>
       <c r="G203" s="3"/>
       <c r="H203" s="3"/>
     </row>
     <row r="204" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="5"/>
-      <c r="B204" s="5"/>
-      <c r="C204" s="5"/>
-      <c r="D204" s="5"/>
-      <c r="E204" s="5"/>
-      <c r="F204" s="5"/>
+      <c r="A204" s="6"/>
+      <c r="B204" s="6"/>
+      <c r="C204" s="6"/>
+      <c r="D204" s="6"/>
+      <c r="E204" s="6"/>
+      <c r="F204" s="6"/>
       <c r="G204" s="3"/>
       <c r="H204" s="3"/>
     </row>
     <row r="205" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="6"/>
-      <c r="B205" s="6"/>
-      <c r="C205" s="6"/>
-      <c r="D205" s="6"/>
-      <c r="E205" s="6"/>
-      <c r="F205" s="6"/>
+      <c r="A205" s="7"/>
+      <c r="B205" s="7"/>
+      <c r="C205" s="7"/>
+      <c r="D205" s="7"/>
+      <c r="E205" s="7"/>
+      <c r="F205" s="7"/>
       <c r="G205" s="3"/>
       <c r="H205" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F205" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="306">
-    <mergeCell ref="E62:E65"/>
-    <mergeCell ref="F194:F197"/>
-    <mergeCell ref="A198:A201"/>
-    <mergeCell ref="C198:C201"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="C130:C133"/>
-    <mergeCell ref="D162:D165"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="C182:C185"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="E182:E185"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="F106:F109"/>
-    <mergeCell ref="A190:A193"/>
-    <mergeCell ref="C150:C153"/>
-    <mergeCell ref="F186:F189"/>
-    <mergeCell ref="C190:C193"/>
-    <mergeCell ref="F170:F173"/>
-    <mergeCell ref="C194:C197"/>
-    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="E130:E133"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="D126:D129"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="E94:E97"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="C178:C181"/>
+    <mergeCell ref="E178:E181"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="C142:C145"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="C162:C165"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="F178:F181"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="E174:E177"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="F138:F141"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="E118:E121"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="D174:D177"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="E202:E205"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="D170:D173"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="D182:D185"/>
+    <mergeCell ref="F182:F185"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="E146:E149"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="D186:D189"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="F202:F205"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="C134:C137"/>
+    <mergeCell ref="E186:E189"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E170:E173"/>
+    <mergeCell ref="F190:F193"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C138:C141"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="E198:E201"/>
+    <mergeCell ref="F166:F169"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="C166:C169"/>
+    <mergeCell ref="F162:F165"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="E190:E193"/>
+    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="D154:D157"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="F154:F157"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="D198:D201"/>
+    <mergeCell ref="F198:F201"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="D58:D61"/>
+    <mergeCell ref="F58:F61"/>
+    <mergeCell ref="E142:E145"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="A202:A205"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="C186:C189"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="B202:B205"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="D178:D181"/>
+    <mergeCell ref="C202:C205"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="D202:D205"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="D166:D169"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="C170:C173"/>
+    <mergeCell ref="F78:F81"/>
+    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="F158:F161"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="F134:F137"/>
+    <mergeCell ref="F146:F149"/>
+    <mergeCell ref="E150:E153"/>
+    <mergeCell ref="F174:F177"/>
+    <mergeCell ref="F126:F129"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="F150:F153"/>
+    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="E154:E157"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="E102:E105"/>
+    <mergeCell ref="F130:F133"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="D142:D145"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="F54:F57"/>
+    <mergeCell ref="C158:C161"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="F86:F89"/>
+    <mergeCell ref="F142:F145"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="D134:D137"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="D130:D133"/>
     <mergeCell ref="D6:D9"/>
     <mergeCell ref="D190:D193"/>
     <mergeCell ref="B86:B89"/>
@@ -4215,266 +4451,30 @@
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="A98:A101"/>
-    <mergeCell ref="F54:F57"/>
-    <mergeCell ref="C158:C161"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="F86:F89"/>
-    <mergeCell ref="F142:F145"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="E98:E101"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="D134:D137"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="D130:D133"/>
-    <mergeCell ref="F130:F133"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="F194:F197"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="C198:C201"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="C130:C133"/>
+    <mergeCell ref="D162:D165"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="C182:C185"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="E182:E185"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="F106:F109"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="C150:C153"/>
+    <mergeCell ref="F186:F189"/>
+    <mergeCell ref="C190:C193"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="C154:C157"/>
     <mergeCell ref="E194:E197"/>
     <mergeCell ref="B150:B153"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="C170:C173"/>
-    <mergeCell ref="F78:F81"/>
-    <mergeCell ref="F118:F121"/>
-    <mergeCell ref="F158:F161"/>
-    <mergeCell ref="D194:D197"/>
-    <mergeCell ref="F134:F137"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A122:A125"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="A202:A205"/>
-    <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="A186:A189"/>
-    <mergeCell ref="C186:C189"/>
-    <mergeCell ref="D94:D97"/>
-    <mergeCell ref="F66:F69"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="E86:E89"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="C146:C149"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="F82:F85"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="D58:D61"/>
-    <mergeCell ref="F58:F61"/>
-    <mergeCell ref="E142:E145"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="B202:B205"/>
-    <mergeCell ref="E198:E201"/>
-    <mergeCell ref="F166:F169"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="C126:C129"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="E126:E129"/>
-    <mergeCell ref="C166:C169"/>
-    <mergeCell ref="F162:F165"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="E190:E193"/>
-    <mergeCell ref="D158:D161"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="D154:D157"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="F154:F157"/>
-    <mergeCell ref="B170:B173"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="C134:C137"/>
-    <mergeCell ref="E186:E189"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="E30:E33"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="A154:A157"/>
-    <mergeCell ref="F102:F105"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E170:E173"/>
-    <mergeCell ref="F190:F193"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C138:C141"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="B174:B177"/>
-    <mergeCell ref="D198:D201"/>
-    <mergeCell ref="F198:F201"/>
-    <mergeCell ref="E202:E205"/>
-    <mergeCell ref="A174:A177"/>
-    <mergeCell ref="D170:D173"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="B198:B201"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="D182:D185"/>
-    <mergeCell ref="F182:F185"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="E106:E109"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="E146:E149"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="E58:E61"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="D186:D189"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="D106:D109"/>
-    <mergeCell ref="F202:F205"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="F146:F149"/>
-    <mergeCell ref="E150:E153"/>
-    <mergeCell ref="D178:D181"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="F74:F77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="F178:F181"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="C202:C205"/>
-    <mergeCell ref="E78:E81"/>
-    <mergeCell ref="B186:B189"/>
-    <mergeCell ref="D102:D105"/>
-    <mergeCell ref="B142:B145"/>
-    <mergeCell ref="D202:D205"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="E174:E177"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="C178:C181"/>
-    <mergeCell ref="E178:E181"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="C142:C145"/>
-    <mergeCell ref="E26:E29"/>
-    <mergeCell ref="D98:D101"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="E66:E69"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="C162:C165"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="F138:F141"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="E118:E121"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A150:A153"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="E130:E133"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E74:E77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="F62:F65"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="D174:D177"/>
-    <mergeCell ref="A178:A181"/>
-    <mergeCell ref="F174:F177"/>
-    <mergeCell ref="D126:D129"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="F126:F129"/>
-    <mergeCell ref="E94:E97"/>
-    <mergeCell ref="D166:D169"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="F150:F153"/>
-    <mergeCell ref="E158:E161"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="E154:E157"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="E102:E105"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="A162:A165"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="D142:D145"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="A146:A149"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/IT23846586-Assignment 1 - Test cases.xlsx
+++ b/IT23846586-Assignment 1 - Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive D\ITPM\assingment 01-submitted\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive D\ITPM\assignment01\test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293E4210-DEE2-4BEB-A0DA-CE4CB7C1E8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9D374-A71C-433E-ADAA-3DBF46107CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -215,13 +215,6 @@
     <t>Neg_0016</t>
   </si>
   <si>
-    <t>mama paasalata yannm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">මම පාසලට යන්නම්
-</t>
-  </si>
-  <si>
     <t>Neg_0017</t>
   </si>
   <si>
@@ -543,24 +536,12 @@
     <t>ඔව්, අපිත් හෙට උදේඑන පටන් ගන්න චාරිකාවට එන්න තමයි හිතාගෙන ඉන්නෙ, කට්ටිය එක්කම යනකොට ගොඩක් විනෝද වෙන්ඩ පුළුවන් නේ.</t>
   </si>
   <si>
-    <t>mama udeta mee dhaws wala aewidhinawa aegatath hodha nisa</t>
-  </si>
-  <si>
-    <t>මම උදේට මේ දවස් වල අැවිධිනව ඇඟටත් හොද නිසා</t>
-  </si>
-  <si>
     <t>oya kade paththe yanawanm, me rasne dawase kanna hoda rasama rasa ice-cream ekak matath aran dennako?</t>
   </si>
   <si>
     <t>ඔය කඩේ පැත්තෙ යනවනම්, මේ රස්නේ දවසේ කන්න හොද රසම රස අයිස් ක්‍රීම් එකක් මටත් අරන් දෙන්නකෝ?</t>
   </si>
   <si>
-    <t>iye raa wela gahapu final cricket match eke anthimata mona team ekada dinuwe kiyala mata poddak kiyanna puluwanda?</t>
-  </si>
-  <si>
-    <t>ඊයේ රෑ වෙලා ගහපු final cricket match එකේ අන්තිමට මොන team එකද දිනුවේ කියලා මට පොඩ්ඩක් කියන්න පුළුවන්ද?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Singlish input types covered </t>
   </si>
   <si>
@@ -576,9 +557,6 @@
     <t>ඔව්, අපිත් හෙට උදෙන්ම පටන් ගන්න චාරිකාවට එන්න තමයි හිතාගෙන ඉන්නේ, කට්ටිය එක්කම යනකොට ගොඩක් විනෝද වෙන්න පුළුවන් නේ.</t>
   </si>
   <si>
-    <t>මම උදේට මේ දවස් වල ඇවිදිනවා ඇඟටත් හොඳ නිසා</t>
-  </si>
-  <si>
     <t>ඔයා කඩේ පැත්තේ යනවනම්, මේ රස්නේ දවසේ කන්න හොඳ රසම රස ice-cream එකක් මටත් අරන් දෙන්නකෝ?</t>
   </si>
   <si>
@@ -600,18 +578,9 @@
     <t>colombo නගරයේ තියෙන හුඟක් අය යන ලොකු සහ ලස්සනම shopping mall එකක් විදිහට One Galle Face එක හඳුන්වන්න පුළුවන්.</t>
   </si>
   <si>
-    <t>ලබන මාසේ අපි පවුලේ කට්ටිය එක්කම දවස් තුනකට අනුරාධපුර වන්දනාවේ යන්න හදන්නේ, ඔයාලත් එනවද අපිත් එක්ක ඒ ගමනට එකතු වෙන්න?</t>
-  </si>
-  <si>
     <t>මම අද හවස office එකේ ඉඳලා ගෙදර එනගමන් රෑ කෑමට කන්න අලුත් පාන් ගෙඩි 2ක් කඩෙන් සල්ලි දීලා අරගෙන ආවා.</t>
   </si>
   <si>
-    <t>හරිම සතුටුයි මේ ලබපු ජයග්‍රහණය ගැන 😍❤️</t>
-  </si>
-  <si>
-    <t>harima sathutui me labapu jayagranaya gana 😍❤️</t>
-  </si>
-  <si>
     <t>mama dan podi office meeting ekaka inne, eka nisa mama meka iwara wuna gamanma tawa winadi 10 kin withara oyata call ekak gannam.</t>
   </si>
   <si>
@@ -630,9 +599,6 @@
     <t>colombo nagaraye thiyena hugak aya yana loku saha lassanama shopping mall ekak widihata One Galle Face eka hadunwanna puluwan.</t>
   </si>
   <si>
-    <t>labana mase api pawule kattiya ekkama dawas thunakata anuradhapura wandanawe yanna hadanne, oyalath enawada apith ekka e gamanata ekathu wenna?</t>
-  </si>
-  <si>
     <t>mama ada hawasa office eke indala gedara enagamna raa kaemata kanna aluth paan gedi 2k kadein salli dila aragena aawa.</t>
   </si>
   <si>
@@ -657,15 +623,6 @@
     <t>මම අද හවස ඔෆිස් එකේ ඉඳල ගෙදර එනගමන් රෑ කෑමට කන්න අලුත් පාන් ගෙඩි 2ක් කඩෙන් සල්ලි දීල අරගෙන ආවා.</t>
   </si>
   <si>
-    <t>හරිම සතුටුයි මේ ලැබපු ජයග්‍රහණය ගැන 😍❤️</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">මම පාසලට යන්න්ම් </t>
-  </si>
-  <si>
     <t xml:space="preserve">එක නම් ගොඩක් හොඩ ඉඩෙඅ එකක්, ලෝකින්ග් ෆොර්වර්ඩ් ටො ඉට් </t>
   </si>
   <si>
@@ -820,6 +777,48 @@
   </si>
   <si>
     <t>Inputs Containing Emojis</t>
+  </si>
+  <si>
+    <t>ohu paminimata godak wela yawee</t>
+  </si>
+  <si>
+    <t>ඔහු පැමිණීමට ගොඩක් වෙලා යාවී</t>
+  </si>
+  <si>
+    <t>ඔහු පමිනිමට ගොඩක් වෙලා යවී</t>
+  </si>
+  <si>
+    <t>ohu pamineemata godak wela yawii</t>
+  </si>
+  <si>
+    <t>ඔහු පැමිණීමට ගොඩක් වෙලා යාවි</t>
+  </si>
+  <si>
+    <t>iyee gahapu match eka wassa nisa DLS method eken thamai dinuma theeranaya unee,overs 40 kata seema una ODI match eka</t>
+  </si>
+  <si>
+    <t>ඊයේ ගහපු match එක වැස්ස නිසා DLS method එකෙන් තමයි දිනුම තීරණය වුණේ, overs 40 කට සීමා වුණ ODI match එක</t>
+  </si>
+  <si>
+    <t>ඊයේ ගහපු match එක වැස්ස නිසා DLS මෙතෝඩ් එකෙන් තමයි දිනුම තීරණය උනේ,overs 40 කට සීමා උනා ODI match එක</t>
+  </si>
+  <si>
+    <t>apee paule wandana charikawa yanna hamadema suudanam wela thiyenne api hithan inne anuradhapura,polonnaruwa wage than keepayakatama gihin wada pudagena enna</t>
+  </si>
+  <si>
+    <t>අපේ පවුලේ වන්දනා චාරිකාව යන්න හැමදේම සූදානම් වෙලා තියෙන්නේ අපි හිතන් ඉන්නේ අනුරාධපුර, පොළොන්නරුව වගේ තැන් කීපයකටම ගිහින් වැඳ පුදාගෙන එන්න</t>
+  </si>
+  <si>
+    <t>අපේ පවුලේ වන්දනා චාරිකාව යන්න හෑමදේම සුදානම් වෙලා තියෙන්නේ අපි හිතන් ඉන්නේ අනුරාධපුර,පොලොන්නරුව වගේ තන් කීපයකටම ගිහින් වඩා පුදාගෙන එන්න</t>
+  </si>
+  <si>
+    <t>harima sathutui me labapu jayagranaya gana 🤙🫶</t>
+  </si>
+  <si>
+    <t>හරිම සතුටුයි මේ ලැබපු ජයග්‍රහණය ගැන</t>
+  </si>
+  <si>
+    <t>හරිම සතුටුයි මේ ලබපු ජයග්‍රහණය ගැන 🤙🫶</t>
   </si>
 </sst>
 </file>
@@ -1304,10 +1303,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1315,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>7</v>
@@ -1330,10 +1329,10 @@
         <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1371,7 +1370,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>12</v>
@@ -1386,10 +1385,10 @@
         <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1427,7 +1426,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>16</v>
@@ -1442,10 +1441,10 @@
         <v>10</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1483,25 +1482,25 @@
         <v>19</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1539,7 +1538,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>21</v>
@@ -1554,10 +1553,10 @@
         <v>10</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1595,7 +1594,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>25</v>
@@ -1610,10 +1609,10 @@
         <v>10</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1651,7 +1650,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>29</v>
@@ -1666,10 +1665,10 @@
         <v>10</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1707,7 +1706,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>33</v>
@@ -1722,10 +1721,10 @@
         <v>10</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1763,7 +1762,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>37</v>
@@ -1778,10 +1777,10 @@
         <v>10</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1819,25 +1818,25 @@
         <v>40</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1875,7 +1874,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>42</v>
@@ -1890,10 +1889,10 @@
         <v>10</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1931,7 +1930,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>46</v>
@@ -1946,10 +1945,10 @@
         <v>10</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1987,7 +1986,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>50</v>
@@ -2002,10 +2001,10 @@
         <v>10</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2043,7 +2042,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>54</v>
@@ -2058,10 +2057,10 @@
         <v>10</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2099,25 +2098,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>168</v>
+        <v>247</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="F58" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="H58" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2155,25 +2154,25 @@
         <v>58</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>59</v>
+        <v>250</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>60</v>
+        <v>248</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2208,28 +2207,28 @@
     </row>
     <row r="66" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C66" s="10" t="s">
+      <c r="E66" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>64</v>
-      </c>
       <c r="F66" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2264,28 +2263,28 @@
     </row>
     <row r="70" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E70" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B70" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="F70" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2320,28 +2319,28 @@
     </row>
     <row r="74" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E74" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="F74" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2376,28 +2375,28 @@
     </row>
     <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2432,28 +2431,28 @@
     </row>
     <row r="82" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>173</v>
+        <v>253</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>173</v>
+        <v>254</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2488,28 +2487,28 @@
     </row>
     <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2544,28 +2543,28 @@
     </row>
     <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D90" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B90" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="E90" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="H90" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2600,28 +2599,28 @@
     </row>
     <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2656,28 +2655,28 @@
     </row>
     <row r="98" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D98" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C98" s="10" t="s">
+      <c r="E98" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="F98" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2712,28 +2711,28 @@
     </row>
     <row r="102" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D102" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B102" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C102" s="10" t="s">
+      <c r="E102" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D102" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="F102" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2768,28 +2767,28 @@
     </row>
     <row r="106" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2824,28 +2823,28 @@
     </row>
     <row r="110" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D110" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B110" s="8" t="s">
+      <c r="E110" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="H110" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2880,28 +2879,28 @@
     </row>
     <row r="114" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D114" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B114" s="8" t="s">
+      <c r="E114" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="H114" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2936,28 +2935,28 @@
     </row>
     <row r="118" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B118" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="H118" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="H118" s="4" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2992,28 +2991,28 @@
     </row>
     <row r="122" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B122" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="H122" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3048,28 +3047,28 @@
     </row>
     <row r="126" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3104,28 +3103,28 @@
     </row>
     <row r="130" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>197</v>
+        <v>255</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3160,28 +3159,28 @@
     </row>
     <row r="134" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D134" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B134" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C134" s="10" t="s">
+      <c r="E134" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D134" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="F134" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3216,28 +3215,28 @@
     </row>
     <row r="138" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D138" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B138" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C138" s="10" t="s">
+      <c r="E138" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D138" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E138" s="5" t="s">
-        <v>106</v>
-      </c>
       <c r="F138" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3272,28 +3271,28 @@
     </row>
     <row r="142" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3328,28 +3327,28 @@
     </row>
     <row r="146" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D146" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B146" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C146" s="10" t="s">
+      <c r="E146" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D146" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="F146" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3384,28 +3383,28 @@
     </row>
     <row r="150" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D150" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B150" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C150" s="10" t="s">
+      <c r="E150" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D150" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="F150" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3440,28 +3439,28 @@
     </row>
     <row r="154" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D154" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B154" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C154" s="10" t="s">
+      <c r="E154" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D154" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E154" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="F154" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3496,28 +3495,28 @@
     </row>
     <row r="158" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D158" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B158" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C158" s="10" t="s">
+      <c r="E158" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D158" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="F158" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3552,28 +3551,28 @@
     </row>
     <row r="162" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D162" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B162" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C162" s="10" t="s">
+      <c r="E162" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D162" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="F162" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3608,28 +3607,28 @@
     </row>
     <row r="166" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D166" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B166" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C166" s="10" t="s">
+      <c r="E166" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D166" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E166" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="F166" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3664,28 +3663,28 @@
     </row>
     <row r="170" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D170" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B170" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C170" s="10" t="s">
+      <c r="E170" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D170" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="F170" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3720,28 +3719,28 @@
     </row>
     <row r="174" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D174" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B174" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C174" s="10" t="s">
+      <c r="E174" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D174" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="F174" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3776,28 +3775,28 @@
     </row>
     <row r="178" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D178" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B178" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C178" s="10" t="s">
+      <c r="E178" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D178" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="F178" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3832,28 +3831,28 @@
     </row>
     <row r="182" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D182" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B182" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C182" s="10" t="s">
+      <c r="E182" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D182" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="F182" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3888,28 +3887,28 @@
     </row>
     <row r="186" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C186" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D186" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B186" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C186" s="10" t="s">
+      <c r="E186" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D186" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E186" s="5" t="s">
-        <v>151</v>
-      </c>
       <c r="F186" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3944,28 +3943,28 @@
     </row>
     <row r="190" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C190" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D190" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B190" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C190" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="D190" s="5" t="s">
-        <v>154</v>
-      </c>
       <c r="E190" s="5" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4000,28 +3999,28 @@
     </row>
     <row r="194" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C194" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D194" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B194" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C194" s="10" t="s">
+      <c r="E194" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D194" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E194" s="5" t="s">
-        <v>158</v>
-      </c>
       <c r="F194" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4056,28 +4055,28 @@
     </row>
     <row r="198" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>189</v>
+        <v>260</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>206</v>
+        <v>259</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>207</v>
+        <v>10</v>
       </c>
       <c r="G198" s="4" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4112,28 +4111,28 @@
     </row>
     <row r="202" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D202" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B202" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C202" s="10" t="s">
+      <c r="E202" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D202" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E202" s="5" t="s">
-        <v>163</v>
-      </c>
       <c r="F202" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/IT23846586-Assignment 1 - Test cases.xlsx
+++ b/IT23846586-Assignment 1 - Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive D\ITPM\assignment01\test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9D374-A71C-433E-ADAA-3DBF46107CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE42A2BC-318C-4B3E-8AC1-1F3D2BDB6E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name=" Test cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">' Test cases'!$A$1:$F$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">' Test cases'!$A$1:$F$197</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="265">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -218,24 +218,9 @@
     <t>Neg_0017</t>
   </si>
   <si>
-    <t>ohu paniwidaya raegena paminewee</t>
-  </si>
-  <si>
-    <t>ඔහු පනිවිඩය රැගෙන පැමිනේවි</t>
-  </si>
-  <si>
-    <t>ඔහු පණිවිඩය රැගෙන පැමිණේවී</t>
-  </si>
-  <si>
     <t>Neg_0018</t>
   </si>
   <si>
-    <t>ohu paniwidaya raegena  paminewi</t>
-  </si>
-  <si>
-    <t>ඔහු පණිවිඩය රැගෙන පැමිණේවි</t>
-  </si>
-  <si>
     <t>Neg_0019</t>
   </si>
   <si>
@@ -779,21 +764,6 @@
     <t>Inputs Containing Emojis</t>
   </si>
   <si>
-    <t>ohu paminimata godak wela yawee</t>
-  </si>
-  <si>
-    <t>ඔහු පැමිණීමට ගොඩක් වෙලා යාවී</t>
-  </si>
-  <si>
-    <t>ඔහු පමිනිමට ගොඩක් වෙලා යවී</t>
-  </si>
-  <si>
-    <t>ohu pamineemata godak wela yawii</t>
-  </si>
-  <si>
-    <t>ඔහු පැමිණීමට ගොඩක් වෙලා යාවි</t>
-  </si>
-  <si>
     <t>iyee gahapu match eka wassa nisa DLS method eken thamai dinuma theeranaya unee,overs 40 kata seema una ODI match eka</t>
   </si>
   <si>
@@ -819,13 +789,61 @@
   </si>
   <si>
     <t>හරිම සතුටුයි මේ ලබපු ජයග්‍රහණය ගැන 🤙🫶</t>
+  </si>
+  <si>
+    <t>ohu paminimata godak wela yawee
+ohu pamineemata godak wela yawii</t>
+  </si>
+  <si>
+    <t>ඔහු පැමිණීමට ගොඩක් වෙලා යාවී
+ඔහු පැමිණීමට ගොඩක් වෙලා යාවී</t>
+  </si>
+  <si>
+    <t>ඔහු පමිනිමට ගොඩක් වෙලා යවී
+ඔහු පැමිණීමට ගොඩක් වෙලා යාවි</t>
+  </si>
+  <si>
+    <t>ohu paniwidaya raegena paminewee
+ohu paniwidaya raegena  paminewi</t>
+  </si>
+  <si>
+    <t>ඔහු පනිවිඩය රැගෙන පැමිනේවි
+ඔහු පනිවිඩය රැගෙන පැමිනේවි</t>
+  </si>
+  <si>
+    <t>ඔහු පණිවිඩය රැගෙන පැමිණේවී
+ඔහු පණිවිඩය රැගෙන පැමිණේවි</t>
+  </si>
+  <si>
+    <t>api kattiyama gedra yanna one nisai pick me car ekak damme</t>
+  </si>
+  <si>
+    <t>අපි කට්ටියම ගෙදර යන්න ඕනේ නිසයි pick me car එකක් දැම්මේ</t>
+  </si>
+  <si>
+    <t>අපි කට්ටියම ගෙදර යන්න ඕනේ නිසයි pick මේ car එකක් දැම්මේ</t>
+  </si>
+  <si>
+    <t>ada dawsa nam niyamai hodata winoda unaaa.🐱</t>
+  </si>
+  <si>
+    <t>අද දවස නම් නියමයි හොඳට විනෝද වුණා. 🐱</t>
+  </si>
+  <si>
+    <t>අද දවස නම් නියමයි හොදට විනෝද උනා.</t>
+  </si>
+  <si>
+    <t>Rationale: Input includes proper wordings like 'pickme'.</t>
+  </si>
+  <si>
+    <t>Rationale: Input uses slang words or casual terms like 'adoo', 'waddek'.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -857,6 +875,12 @@
       <color theme="1"/>
       <name val="Iskoola Pota"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -947,28 +971,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -979,9 +997,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -990,6 +1005,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1303,36 +1327,36 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1366,29 +1390,29 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1422,29 +1446,29 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1478,85 +1502,85 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F14" s="18" t="s">
+      <c r="B14" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="16"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="16"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="17"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B18" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1590,29 +1614,29 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="B22" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1646,29 +1670,29 @@
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1702,29 +1726,29 @@
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1758,29 +1782,29 @@
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C34" s="10" t="s">
+      <c r="B34" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1814,29 +1838,29 @@
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="H38" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1870,29 +1894,29 @@
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C42" s="10" t="s">
+      <c r="B42" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1926,29 +1950,29 @@
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C46" s="10" t="s">
+      <c r="B46" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1982,29 +2006,29 @@
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C50" s="10" t="s">
+      <c r="B50" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C50" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2038,29 +2062,29 @@
       <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C54" s="10" t="s">
+      <c r="B54" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C54" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D54" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2094,29 +2118,29 @@
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F58" s="8" t="s">
+      <c r="B58" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F58" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2150,29 +2174,29 @@
       <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="F62" s="8" t="s">
+      <c r="B62" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="F62" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2206,29 +2230,29 @@
       <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E66" s="5" t="s">
+      <c r="B66" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C66" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F66" s="8" t="s">
+      <c r="D66" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F66" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2262,29 +2286,29 @@
       <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F70" s="8" t="s">
+      <c r="A70" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F70" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2318,29 +2342,29 @@
       <c r="H73" s="4"/>
     </row>
     <row r="74" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F74" s="8" t="s">
+      <c r="A74" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F74" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2374,29 +2398,29 @@
       <c r="H77" s="4"/>
     </row>
     <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F78" s="8" t="s">
+      <c r="A78" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F78" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2430,29 +2454,29 @@
       <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F82" s="8" t="s">
+      <c r="A82" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="F82" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2486,29 +2510,29 @@
       <c r="H85" s="4"/>
     </row>
     <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F86" s="8" t="s">
+      <c r="A86" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F86" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2542,29 +2566,29 @@
       <c r="H89" s="4"/>
     </row>
     <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C90" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B90" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C90" s="10" t="s">
+      <c r="D90" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="E90" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E90" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F90" s="8" t="s">
+      <c r="F90" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2598,29 +2622,29 @@
       <c r="H93" s="4"/>
     </row>
     <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F94" s="8" t="s">
+      <c r="A94" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F94" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2654,29 +2678,29 @@
       <c r="H97" s="4"/>
     </row>
     <row r="98" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F98" s="8" t="s">
+      <c r="A98" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F98" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2710,29 +2734,29 @@
       <c r="H101" s="4"/>
     </row>
     <row r="102" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C102" s="10" t="s">
+      <c r="A102" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C102" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D102" s="5" t="s">
+      <c r="D102" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E102" s="5" t="s">
+      <c r="E102" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F102" s="8" t="s">
+      <c r="F102" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2766,29 +2790,29 @@
       <c r="H105" s="4"/>
     </row>
     <row r="106" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="F106" s="8" t="s">
+      <c r="A106" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F106" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2822,29 +2846,29 @@
       <c r="H109" s="4"/>
     </row>
     <row r="110" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B110" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F110" s="8" t="s">
+      <c r="A110" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F110" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2878,29 +2902,29 @@
       <c r="H113" s="4"/>
     </row>
     <row r="114" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B114" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F114" s="8" t="s">
+      <c r="A114" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="F114" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2934,29 +2958,29 @@
       <c r="H117" s="4"/>
     </row>
     <row r="118" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B118" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="F118" s="8" t="s">
+      <c r="A118" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F118" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2990,29 +3014,29 @@
       <c r="H121" s="4"/>
     </row>
     <row r="122" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B122" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="F122" s="8" t="s">
+      <c r="A122" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F122" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3046,29 +3070,29 @@
       <c r="H125" s="4"/>
     </row>
     <row r="126" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="9" t="s">
+      <c r="A126" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B126" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E126" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B126" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C126" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F126" s="8" t="s">
+      <c r="F126" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3102,29 +3126,29 @@
       <c r="H129" s="4"/>
     </row>
     <row r="130" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B130" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C130" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="F130" s="8" t="s">
+      <c r="A130" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F130" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3158,29 +3182,29 @@
       <c r="H133" s="4"/>
     </row>
     <row r="134" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C134" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F134" s="8" t="s">
+      <c r="A134" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C134" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F134" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3214,29 +3238,29 @@
       <c r="H137" s="4"/>
     </row>
     <row r="138" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B138" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C138" s="10" t="s">
+      <c r="A138" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C138" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D138" s="5" t="s">
+      <c r="D138" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E138" s="5" t="s">
+      <c r="E138" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F138" s="8" t="s">
+      <c r="F138" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3270,29 +3294,29 @@
       <c r="H141" s="4"/>
     </row>
     <row r="142" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B142" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C142" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F142" s="8" t="s">
+      <c r="A142" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C142" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F142" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3326,29 +3350,29 @@
       <c r="H145" s="4"/>
     </row>
     <row r="146" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B146" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C146" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F146" s="8" t="s">
+      <c r="A146" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F146" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3382,29 +3406,29 @@
       <c r="H149" s="4"/>
     </row>
     <row r="150" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B150" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C150" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F150" s="8" t="s">
+      <c r="A150" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C150" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F150" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3438,29 +3462,29 @@
       <c r="H153" s="4"/>
     </row>
     <row r="154" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B154" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C154" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E154" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F154" s="8" t="s">
+      <c r="A154" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C154" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F154" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3494,29 +3518,29 @@
       <c r="H157" s="4"/>
     </row>
     <row r="158" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B158" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C158" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D158" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F158" s="8" t="s">
+      <c r="A158" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C158" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F158" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3550,29 +3574,29 @@
       <c r="H161" s="4"/>
     </row>
     <row r="162" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B162" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C162" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D162" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F162" s="8" t="s">
+      <c r="A162" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F162" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3606,29 +3630,29 @@
       <c r="H165" s="4"/>
     </row>
     <row r="166" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="B166" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C166" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D166" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E166" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F166" s="8" t="s">
+      <c r="A166" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C166" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="F166" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3662,29 +3686,29 @@
       <c r="H169" s="4"/>
     </row>
     <row r="170" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B170" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C170" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D170" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F170" s="8" t="s">
+      <c r="A170" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B170" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C170" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F170" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3718,29 +3742,29 @@
       <c r="H173" s="4"/>
     </row>
     <row r="174" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B174" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C174" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F174" s="8" t="s">
+      <c r="A174" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C174" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F174" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3774,29 +3798,29 @@
       <c r="H177" s="4"/>
     </row>
     <row r="178" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B178" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C178" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="D178" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F178" s="8" t="s">
+      <c r="A178" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C178" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F178" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3830,29 +3854,29 @@
       <c r="H181" s="4"/>
     </row>
     <row r="182" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B182" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C182" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D182" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F182" s="8" t="s">
+      <c r="A182" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C182" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="F182" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3886,29 +3910,29 @@
       <c r="H185" s="4"/>
     </row>
     <row r="186" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="B186" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C186" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D186" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E186" s="5" t="s">
+      <c r="A186" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C186" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F186" s="8" t="s">
+      <c r="D186" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F186" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3942,29 +3966,29 @@
       <c r="H189" s="4"/>
     </row>
     <row r="190" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B190" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C190" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="D190" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F190" s="8" t="s">
+      <c r="A190" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C190" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F190" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3998,29 +4022,29 @@
       <c r="H193" s="4"/>
     </row>
     <row r="194" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="B194" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C194" s="10" t="s">
+      <c r="A194" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C194" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D194" s="5" t="s">
+      <c r="D194" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="E194" s="5" t="s">
+      <c r="E194" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="F194" s="8" t="s">
+      <c r="F194" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4030,8 +4054,8 @@
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
       <c r="F195" s="6"/>
-      <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
+      <c r="G195" s="3"/>
+      <c r="H195" s="3"/>
     </row>
     <row r="196" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6"/>
@@ -4040,8 +4064,8 @@
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
       <c r="F196" s="6"/>
-      <c r="G196" s="4"/>
-      <c r="H196" s="4"/>
+      <c r="G196" s="3"/>
+      <c r="H196" s="3"/>
     </row>
     <row r="197" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="7"/>
@@ -4050,33 +4074,33 @@
       <c r="D197" s="7"/>
       <c r="E197" s="7"/>
       <c r="F197" s="7"/>
-      <c r="G197" s="4"/>
-      <c r="H197" s="4"/>
+      <c r="G197" s="3"/>
+      <c r="H197" s="3"/>
     </row>
     <row r="198" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B198" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C198" s="10" t="s">
+      <c r="A198" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C198" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D198" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="D198" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="E198" s="5" t="s">
+      <c r="E198" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="F198" s="8" t="s">
+      <c r="F198" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G198" s="4" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>223</v>
+        <v>263</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4086,8 +4110,8 @@
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
       <c r="F199" s="6"/>
-      <c r="G199" s="4"/>
-      <c r="H199" s="4"/>
+      <c r="G199" s="3"/>
+      <c r="H199" s="3"/>
     </row>
     <row r="200" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6"/>
@@ -4096,8 +4120,8 @@
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
       <c r="F200" s="6"/>
-      <c r="G200" s="4"/>
-      <c r="H200" s="4"/>
+      <c r="G200" s="3"/>
+      <c r="H200" s="3"/>
     </row>
     <row r="201" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="7"/>
@@ -4106,33 +4130,33 @@
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
-      <c r="G201" s="4"/>
-      <c r="H201" s="4"/>
+      <c r="G201" s="3"/>
+      <c r="H201" s="3"/>
     </row>
     <row r="202" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="B202" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C202" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="D202" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E202" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="F202" s="8" t="s">
+      <c r="A202" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D202" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="F202" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4166,190 +4190,144 @@
       <c r="H205" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F205" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F197" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="306">
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="C198:C201"/>
+    <mergeCell ref="D198:D201"/>
+    <mergeCell ref="E198:E201"/>
+    <mergeCell ref="F198:F201"/>
+    <mergeCell ref="A202:A205"/>
+    <mergeCell ref="B202:B205"/>
+    <mergeCell ref="C202:C205"/>
+    <mergeCell ref="D202:D205"/>
+    <mergeCell ref="E202:E205"/>
+    <mergeCell ref="F202:F205"/>
+    <mergeCell ref="F186:F189"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="C190:C193"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="D154:D157"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="C174:C177"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="E174:E177"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="C142:C145"/>
+    <mergeCell ref="F178:F181"/>
+    <mergeCell ref="C182:C185"/>
+    <mergeCell ref="F162:F165"/>
+    <mergeCell ref="C186:C189"/>
+    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="E186:E189"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="D182:D185"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="C166:C169"/>
+    <mergeCell ref="B182:B185"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="E154:E157"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="D130:D133"/>
+    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="D134:D137"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="F54:F57"/>
+    <mergeCell ref="C150:C153"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="F78:F81"/>
+    <mergeCell ref="F134:F137"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="D126:D129"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="C162:C165"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="F150:F153"/>
+    <mergeCell ref="D186:D189"/>
+    <mergeCell ref="F126:F129"/>
+    <mergeCell ref="F138:F141"/>
+    <mergeCell ref="E142:E145"/>
+    <mergeCell ref="F166:F169"/>
+    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="F142:F145"/>
+    <mergeCell ref="E150:E153"/>
+    <mergeCell ref="E146:E149"/>
+    <mergeCell ref="E102:E105"/>
+    <mergeCell ref="F86:F89"/>
+    <mergeCell ref="E94:E97"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="C178:C181"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="B194:B197"/>
     <mergeCell ref="B114:B117"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A122:A125"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="D170:D173"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="D142:D145"/>
     <mergeCell ref="B158:B161"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A150:A153"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="E130:E133"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="E74:E77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="D126:D129"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="E94:E97"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="C178:C181"/>
-    <mergeCell ref="E178:E181"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="C142:C145"/>
-    <mergeCell ref="E26:E29"/>
-    <mergeCell ref="D98:D101"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="E66:E69"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="C162:C165"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="F74:F77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="F178:F181"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="D138:D141"/>
     <mergeCell ref="E78:E81"/>
-    <mergeCell ref="D102:D105"/>
-    <mergeCell ref="B142:B145"/>
-    <mergeCell ref="E174:E177"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="F138:F141"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="E118:E121"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="F62:F65"/>
-    <mergeCell ref="D174:D177"/>
-    <mergeCell ref="F66:F69"/>
-    <mergeCell ref="E202:E205"/>
-    <mergeCell ref="A174:A177"/>
-    <mergeCell ref="D170:D173"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="B198:B201"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="D182:D185"/>
-    <mergeCell ref="F182:F185"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="E106:E109"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="E146:E149"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="E58:E61"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="D186:D189"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="D106:D109"/>
-    <mergeCell ref="F202:F205"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="C134:C137"/>
-    <mergeCell ref="E186:E189"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="E30:E33"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="A154:A157"/>
-    <mergeCell ref="F102:F105"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E170:E173"/>
-    <mergeCell ref="F190:F193"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C138:C141"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="B174:B177"/>
-    <mergeCell ref="E198:E201"/>
-    <mergeCell ref="F166:F169"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="C126:C129"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="E126:E129"/>
-    <mergeCell ref="C166:C169"/>
-    <mergeCell ref="F162:F165"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="E190:E193"/>
-    <mergeCell ref="D158:D161"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="D154:D157"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="F154:F157"/>
-    <mergeCell ref="B170:B173"/>
-    <mergeCell ref="D198:D201"/>
-    <mergeCell ref="F198:F201"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="E86:E89"/>
     <mergeCell ref="F10:F13"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C22:C25"/>
     <mergeCell ref="F18:F21"/>
-    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="C138:C141"/>
     <mergeCell ref="F30:F33"/>
     <mergeCell ref="E38:E41"/>
     <mergeCell ref="C30:C33"/>
-    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="F74:F77"/>
     <mergeCell ref="C14:C17"/>
-    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="C90:C93"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="F26:F29"/>
     <mergeCell ref="D10:D13"/>
@@ -4357,124 +4335,171 @@
     <mergeCell ref="C38:C41"/>
     <mergeCell ref="D58:D61"/>
     <mergeCell ref="F58:F61"/>
-    <mergeCell ref="E142:E145"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="A202:A205"/>
+    <mergeCell ref="E134:E137"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="E190:E193"/>
+    <mergeCell ref="F158:F161"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="E118:E121"/>
+    <mergeCell ref="C158:C161"/>
+    <mergeCell ref="F154:F157"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="E130:E133"/>
+    <mergeCell ref="E182:E185"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="F106:F109"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="F146:F149"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="D190:D193"/>
+    <mergeCell ref="F190:F193"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="E178:E181"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E162:E165"/>
+    <mergeCell ref="F182:F185"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C130:C133"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="E194:E197"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="D162:D165"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="D174:D177"/>
+    <mergeCell ref="F174:F177"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="D178:D181"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="F194:F197"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="E166:E169"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="F130:F133"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="D166:D169"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="C170:C173"/>
+    <mergeCell ref="E170:E173"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="C134:C137"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="A34:A37"/>
     <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="A186:A189"/>
-    <mergeCell ref="C186:C189"/>
-    <mergeCell ref="D94:D97"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="B202:B205"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="D178:D181"/>
-    <mergeCell ref="C202:C205"/>
-    <mergeCell ref="B186:B189"/>
-    <mergeCell ref="D202:D205"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="A178:A181"/>
-    <mergeCell ref="D166:D169"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="D34:D37"/>
     <mergeCell ref="A114:A117"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="C170:C173"/>
-    <mergeCell ref="F78:F81"/>
-    <mergeCell ref="F118:F121"/>
-    <mergeCell ref="F158:F161"/>
-    <mergeCell ref="D194:D197"/>
-    <mergeCell ref="F134:F137"/>
-    <mergeCell ref="F146:F149"/>
-    <mergeCell ref="E150:E153"/>
-    <mergeCell ref="F174:F177"/>
-    <mergeCell ref="F126:F129"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="F150:F153"/>
-    <mergeCell ref="E158:E161"/>
-    <mergeCell ref="E154:E157"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="E102:E105"/>
-    <mergeCell ref="F130:F133"/>
-    <mergeCell ref="A162:A165"/>
-    <mergeCell ref="D142:D145"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="F54:F57"/>
-    <mergeCell ref="C158:C161"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="F86:F89"/>
-    <mergeCell ref="F142:F145"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="E98:E101"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="D134:D137"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="D130:D133"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="D190:D193"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="A138:A141"/>
-    <mergeCell ref="E82:E85"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="B182:B185"/>
-    <mergeCell ref="B154:B157"/>
-    <mergeCell ref="C174:C177"/>
-    <mergeCell ref="B190:B193"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="E162:E165"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A134:A137"/>
-    <mergeCell ref="B162:B165"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="B138:B141"/>
-    <mergeCell ref="E134:E137"/>
-    <mergeCell ref="D138:D141"/>
-    <mergeCell ref="E166:E169"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="E62:E65"/>
-    <mergeCell ref="F194:F197"/>
-    <mergeCell ref="A198:A201"/>
-    <mergeCell ref="C198:C201"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="C130:C133"/>
-    <mergeCell ref="D162:D165"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="C182:C185"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="E182:E185"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="F106:F109"/>
-    <mergeCell ref="A190:A193"/>
-    <mergeCell ref="C150:C153"/>
-    <mergeCell ref="F186:F189"/>
-    <mergeCell ref="C190:C193"/>
-    <mergeCell ref="F170:F173"/>
-    <mergeCell ref="C194:C197"/>
-    <mergeCell ref="C154:C157"/>
-    <mergeCell ref="E194:E197"/>
-    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B22:B25"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>